--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486427_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486427_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2841</v>
+        <v>4.0606</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6481</v>
+        <v>4.4246</v>
       </c>
       <c r="F2" t="n">
         <v>-0.364</v>
@@ -610,10 +610,10 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06850000000000001</v>
+        <v>-0.155</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9542</v>
+        <v>0.7306</v>
       </c>
       <c r="U2" t="n">
         <v>-0.8857</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0235</v>
+        <v>2.7433</v>
       </c>
       <c r="E3" t="n">
-        <v>0.384</v>
+        <v>1.0113</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6395</v>
+        <v>1.7319</v>
       </c>
       <c r="G3" t="n">
         <v>0.0939</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7399</v>
+        <v>-0.0201</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6609</v>
+        <v>-0.0336</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.079</v>
+        <v>0.0135</v>
       </c>
       <c r="V3" t="n">
         <v>1.582</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1296</v>
+        <v>0.207</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6099</v>
+        <v>1.2349</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5196</v>
+        <v>-1.0279</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3764</v>
+        <v>1.9425</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7876</v>
+        <v>0.1703</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4112</v>
+        <v>1.7722</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0017</v>
+        <v>2.8152</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1547</v>
+        <v>1.5147</v>
       </c>
       <c r="L4" t="n">
-        <v>0.153</v>
+        <v>1.3005</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3747</v>
+        <v>-0.8727</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6328</v>
+        <v>-1.3444</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2582</v>
+        <v>0.4717</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6784</v>
+        <v>-0.015</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6117</v>
+        <v>-0.4927</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0667</v>
+        <v>0.4777</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.695</v>
+        <v>-2.3729</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.695</v>
+        <v>-2.3729</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2117</v>
+        <v>0.1268</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0547</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.843</v>
+        <v>0.1189</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9425</v>
+        <v>-0.3764</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1703</v>
+        <v>-0.7876</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7722</v>
+        <v>0.4112</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8152</v>
+        <v>-0.0017</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5147</v>
+        <v>-0.1547</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3005</v>
+        <v>0.153</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8727</v>
+        <v>-0.3747</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3444</v>
+        <v>-0.6328</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4717</v>
+        <v>0.2582</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0103</v>
+        <v>0.6757</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6626</v>
+        <v>0.666</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.3729</v>
+        <v>-1.695</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3729</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1777</v>
+        <v>-1.6932</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6767</v>
+        <v>-1.6223</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.501</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.11</v>
+        <v>-3.9238</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0032</v>
+        <v>-2.6489</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1131</v>
+        <v>-1.2749</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4997</v>
+        <v>-3.4981</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3467</v>
+        <v>-2.0495</v>
       </c>
       <c r="L6" t="n">
-        <v>0.153</v>
+        <v>-1.4486</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3898</v>
+        <v>-0.4257</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3499</v>
+        <v>-0.5994</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0399</v>
+        <v>0.1737</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5225</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3926</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6731</v>
+        <v>0.1027</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2161</v>
+        <v>-0.2944</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5431</v>
+        <v>0.3972</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4382</v>
+        <v>3.2154</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>4.3454</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4382</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2704</v>
+        <v>-1.9196</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1378</v>
+        <v>-1.5987</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1326</v>
+        <v>-0.321</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.9238</v>
+        <v>-0.3997</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.6489</v>
+        <v>-0.9734</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2749</v>
+        <v>0.5737</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.4981</v>
+        <v>1.0691</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.0495</v>
+        <v>0.073</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4486</v>
+        <v>0.9961</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4257</v>
+        <v>-1.4688</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5994</v>
+        <v>-1.0464</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1737</v>
+        <v>-0.4224</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0875</v>
+        <v>2.3926</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4744</v>
+        <v>-0.4945</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8099</v>
+        <v>-0.4927</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3355</v>
+        <v>-0.0018</v>
       </c>
       <c r="V7" t="n">
-        <v>3.2154</v>
+        <v>-1.243</v>
       </c>
       <c r="W7" t="n">
-        <v>4.3454</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2848</v>
+        <v>-2.6322</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7789</v>
+        <v>-1.2372</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5059</v>
+        <v>-1.395</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3997</v>
+        <v>-2.5757</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9734</v>
+        <v>-1.7215</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5737</v>
+        <v>-0.8542</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0691</v>
+        <v>-1.2065</v>
       </c>
       <c r="K8" t="n">
-        <v>0.073</v>
+        <v>-0.5411</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9961</v>
+        <v>-0.6653</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4688</v>
+        <v>-1.3692</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0464</v>
+        <v>-1.1803</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4224</v>
+        <v>-0.1889</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8597</v>
+        <v>-0.9043</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1867</v>
+        <v>-0.8959</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.243</v>
+        <v>0.1952</v>
       </c>
       <c r="W8" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.243</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6938</v>
+        <v>-2.7057</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2372</v>
+        <v>-1.2355</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4567</v>
+        <v>-1.4702</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5757</v>
+        <v>0.11</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7215</v>
+        <v>-0.0032</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8542</v>
+        <v>0.1131</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2065</v>
+        <v>0.4997</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5411</v>
+        <v>0.3467</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6653</v>
+        <v>0.153</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3692</v>
+        <v>-0.3898</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1803</v>
+        <v>-0.3499</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1889</v>
+        <v>-0.0399</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R9" t="n">
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9659</v>
+        <v>0.1451</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.6573</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9575</v>
+        <v>-0.5122</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1952</v>
+        <v>-1.4382</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4382</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0121</v>
+        <v>-3.4283</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.579</v>
+        <v>-2.026</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4331</v>
+        <v>-1.4023</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9844000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0924</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4831</v>
+        <v>0.0361</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5755</v>
+        <v>-0.5447</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>T. ROBERTS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0333</v>
+        <v>-3.7079</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3134</v>
+        <v>-2.6817</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7199</v>
+        <v>-1.0262</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6754</v>
+        <v>-0.3396</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.567</v>
+        <v>-1.2226</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1084</v>
+        <v>0.883</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0567</v>
+        <v>0.534</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5411</v>
+        <v>-0.3888</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5155999999999999</v>
+        <v>0.9228</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6187</v>
+        <v>-0.8736</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.0258</v>
+        <v>-0.8337</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4072</v>
+        <v>-0.0399</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5225</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3926</v>
+        <v>-3.4801</v>
       </c>
       <c r="R11" t="n">
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3391</v>
+        <v>-0.7583</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6802</v>
+        <v>0.2644</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3411</v>
+        <v>-1.0227</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. ROBERTS</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0836</v>
+        <v>-4.6152</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6875</v>
+        <v>-3.6487</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3961</v>
+        <v>-0.9665</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3396</v>
+        <v>-2.6754</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2226</v>
+        <v>-2.567</v>
       </c>
       <c r="I12" t="n">
-        <v>0.883</v>
+        <v>-0.1084</v>
       </c>
       <c r="J12" t="n">
-        <v>0.534</v>
+        <v>-1.0567</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3888</v>
+        <v>-0.5411</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9228</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8736</v>
+        <v>-1.6187</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8337</v>
+        <v>-2.0258</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0399</v>
+        <v>0.4072</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.6101</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4801</v>
+        <v>-2.3926</v>
       </c>
       <c r="R12" t="n">
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.134</v>
+        <v>-0.2427</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.3449</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3925</v>
+        <v>-0.5876</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.9068</v>
+        <v>-13.5644</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.713799999999999</v>
+        <v>-7.3714</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.193199999999999</v>
+        <v>-6.1933</v>
       </c>
       <c r="G13" t="n">
         <v>-6.2997</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.702399999999999</v>
+        <v>-9.702400000000001</v>
       </c>
       <c r="I13" t="n">
         <v>3.4026</v>
@@ -1468,13 +1468,13 @@
         <v>14.1378</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5175</v>
+        <v>-2.175</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3788999999999999</v>
+        <v>0.7211000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.8963</v>
+        <v>-2.8962</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7394999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4065</v>
+        <v>6.4617</v>
       </c>
       <c r="E14" t="n">
-        <v>7.4818</v>
+        <v>7.1465</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0753</v>
+        <v>-0.6848</v>
       </c>
       <c r="G14" t="n">
         <v>4.0468</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5772</v>
+        <v>0.6324</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9542</v>
+        <v>0.6189</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.377</v>
+        <v>0.0135</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6255</v>
+        <v>4.7046</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6822</v>
+        <v>3.1868</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9433</v>
+        <v>1.5178</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9008</v>
+        <v>1.6312</v>
       </c>
       <c r="H15" t="n">
-        <v>0.657</v>
+        <v>1.6973</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2438</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1941</v>
+        <v>2.052</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8244</v>
+        <v>2.0138</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6303</v>
+        <v>0.0382</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7067</v>
+        <v>-0.4208</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1674</v>
+        <v>-0.3164</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8741</v>
+        <v>-0.1044</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8546</v>
+        <v>0.4209</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5756</v>
+        <v>0.2223</v>
       </c>
       <c r="U15" t="n">
-        <v>0.279</v>
+        <v>0.1986</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2992</v>
+        <v>4.6126</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8788</v>
+        <v>1.4587</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4204</v>
+        <v>3.154</v>
       </c>
       <c r="G16" t="n">
-        <v>0.455</v>
+        <v>0.9008</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2503</v>
+        <v>0.657</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7953</v>
+        <v>0.2438</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4288</v>
+        <v>0.1941</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2687</v>
+        <v>0.8244</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8399</v>
+        <v>-0.6303</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0262</v>
+        <v>0.7067</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0184</v>
+        <v>-0.1674</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0446</v>
+        <v>0.8741</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6919</v>
+        <v>0.8418</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4951</v>
+        <v>0.3521</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1968</v>
+        <v>0.4897</v>
       </c>
       <c r="V16" t="n">
-        <v>2.0647</v>
+        <v>1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2599</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2769</v>
+        <v>4.0141</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8515</v>
+        <v>1.6553</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4253</v>
+        <v>2.3587</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6312</v>
+        <v>0.455</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6973</v>
+        <v>1.2503</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.7953</v>
       </c>
       <c r="J17" t="n">
-        <v>2.052</v>
+        <v>0.4288</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0138</v>
+        <v>1.2687</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0382</v>
+        <v>-0.8399</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4208</v>
+        <v>0.0262</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3164</v>
+        <v>-0.0184</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1044</v>
+        <v>0.0446</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0068</v>
+        <v>0.4068</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.113</v>
+        <v>0.2716</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1061</v>
+        <v>0.1352</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>2.0647</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.4498</v>
+        <v>2.914</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8091</v>
+        <v>0.0268</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6406</v>
+        <v>2.8872</v>
       </c>
       <c r="G18" t="n">
         <v>0.1617</v>
@@ -1858,13 +1858,13 @@
         <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>0.591</v>
+        <v>0.0553</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9542</v>
+        <v>0.1719</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3632</v>
+        <v>-0.1166</v>
       </c>
       <c r="V18" t="n">
         <v>0.7395</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7884</v>
+        <v>0.7964</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8396</v>
+        <v>0.0805</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0511</v>
+        <v>0.7159</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3296</v>
+        <v>0.596</v>
       </c>
       <c r="H19" t="n">
-        <v>0.292</v>
+        <v>0.447</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6216</v>
+        <v>0.149</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8946</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6268</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2677</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2241</v>
+        <v>0.596</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3348</v>
+        <v>0.447</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8893</v>
+        <v>0.149</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2501</v>
+        <v>-0.0171</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8172</v>
+        <v>0.0805</v>
       </c>
       <c r="U19" t="n">
-        <v>0.433</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.2272</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0805</v>
+        <v>0.5043</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6851</v>
+        <v>-0.2771</v>
       </c>
       <c r="G20" t="n">
-        <v>0.596</v>
+        <v>-0.3296</v>
       </c>
       <c r="H20" t="n">
-        <v>0.447</v>
+        <v>0.292</v>
       </c>
       <c r="I20" t="n">
-        <v>0.149</v>
+        <v>-0.6216</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.8946</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.6268</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.2677</v>
       </c>
       <c r="M20" t="n">
-        <v>0.596</v>
+        <v>-1.2241</v>
       </c>
       <c r="N20" t="n">
-        <v>0.447</v>
+        <v>-0.3348</v>
       </c>
       <c r="O20" t="n">
-        <v>0.149</v>
+        <v>-0.8893</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0479</v>
+        <v>0.6889</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0805</v>
+        <v>0.4819</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1285</v>
+        <v>0.207</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7614</v>
+        <v>-0.3452</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.717</v>
+        <v>-1.27</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9556</v>
+        <v>0.9248</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3128</v>
@@ -2092,13 +2092,13 @@
         <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1011</v>
+        <v>0.3151</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1694</v>
+        <v>0.2776</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0684</v>
+        <v>0.0375</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9568</v>
+        <v>-0.9362</v>
       </c>
       <c r="E22" t="n">
         <v>-1.6407</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6839</v>
+        <v>0.7045</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3871</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4075</v>
+        <v>0.4281</v>
       </c>
       <c r="T22" t="n">
         <v>0.1526</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2549</v>
+        <v>0.2755</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4997</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SPEIGHT</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2882</v>
+        <v>-2.1519</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6686</v>
+        <v>-1.7491</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3804</v>
+        <v>-0.4028</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0492</v>
+        <v>2.4742</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9159</v>
+        <v>2.0558</v>
       </c>
       <c r="I23" t="n">
-        <v>1.965</v>
+        <v>0.4184</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5904</v>
+        <v>2.5349</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.648</v>
+        <v>1.8432</v>
       </c>
       <c r="L23" t="n">
-        <v>2.2384</v>
+        <v>0.6917</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5412</v>
+        <v>-0.0607</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2679</v>
+        <v>0.2127</v>
       </c>
       <c r="O23" t="n">
         <v>-0.2733</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5225</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6976</v>
+        <v>-4.3501</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5104</v>
+        <v>0.0916</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4386</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0717</v>
+        <v>0.0255</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.3252</v>
+        <v>-1.8902</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.3252</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>M. SPEIGHT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1873</v>
+        <v>-2.3434</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4197</v>
+        <v>-2.7804</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7675999999999999</v>
+        <v>0.4369</v>
       </c>
       <c r="G24" t="n">
-        <v>2.4742</v>
+        <v>0.0492</v>
       </c>
       <c r="H24" t="n">
-        <v>2.0558</v>
+        <v>-1.9159</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4184</v>
+        <v>1.965</v>
       </c>
       <c r="J24" t="n">
-        <v>2.5349</v>
+        <v>0.5904</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8432</v>
+        <v>-1.648</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6917</v>
+        <v>2.2384</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0607</v>
+        <v>-0.5412</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2127</v>
+        <v>-0.2679</v>
       </c>
       <c r="O24" t="n">
         <v>-0.2733</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.8276</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.3501</v>
+        <v>-3.6976</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9437</v>
+        <v>0.4551</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6044</v>
+        <v>0.3269</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3392</v>
+        <v>0.1283</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8902</v>
+        <v>-1.3252</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.8902</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5112</v>
+        <v>-2.5568</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.4256</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5269</v>
+        <v>-2.1313</v>
       </c>
       <c r="G25" t="n">
         <v>-0.9857</v>
@@ -2404,13 +2404,13 @@
         <v>0.6525</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2656</v>
+        <v>-0.3112</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.1262</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5807</v>
+        <v>-0.1851</v>
       </c>
       <c r="V25" t="n">
         <v>-1.695</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>13.907</v>
+        <v>15.3971</v>
       </c>
       <c r="E26" t="n">
-        <v>6.193099999999998</v>
+        <v>6.193099999999997</v>
       </c>
       <c r="F26" t="n">
-        <v>7.713699999999999</v>
+        <v>9.203799999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>6.299700000000001</v>
+        <v>6.2997</v>
       </c>
       <c r="H26" t="n">
         <v>9.702199999999998</v>
@@ -2455,7 +2455,7 @@
         <v>-3.4027</v>
       </c>
       <c r="J26" t="n">
-        <v>9.309299999999999</v>
+        <v>9.3093</v>
       </c>
       <c r="K26" t="n">
         <v>9.978400000000001</v>
@@ -2467,13 +2467,13 @@
         <v>-3.0096</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2759999999999999</v>
+        <v>-0.2760000000000001</v>
       </c>
       <c r="O26" t="n">
         <v>-2.7334</v>
       </c>
       <c r="P26" t="n">
-        <v>4.3501</v>
+        <v>4.350099999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-14.1378</v>
@@ -2482,13 +2482,13 @@
         <v>18.4882</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5176</v>
+        <v>4.0077</v>
       </c>
       <c r="T26" t="n">
         <v>2.8962</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3787</v>
+        <v>1.1115</v>
       </c>
       <c r="V26" t="n">
         <v>0.7394999999999998</v>
@@ -2497,7 +2497,7 @@
         <v>8.1257</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.3863</v>
+        <v>-7.386299999999999</v>
       </c>
     </row>
   </sheetData>
